--- a/sheets/종합인생라인.xlsx
+++ b/sheets/종합인생라인.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>생성일 2026-06-23 · 2026~2040</t>
+          <t>생성일 2026-07-02 · 2026~2040</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>월 628,032원</t>
+          <t>월 735,081원</t>
         </is>
       </c>
     </row>
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4083333</v>
+        <v>4331351</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>48999996</v>
+        <v>51976212</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>614520</v>
+        <v>102777</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>614520</v>
+        <v>102777</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>16279689</v>
+        <v>17928921</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>16279689</v>
+        <v>17928921</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>7월 현철 월급만 · 8월 여친 첫 급여·자산분배 · 저축 루틴 시작</t>
+          <t>5/18 입사 · 7/1 여친 근무 · 8월~ 여친 소득 · 10월~ 가구 470만</t>
         </is>
       </c>
     </row>
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4576000</v>
+        <v>4886473</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>54912000</v>
+        <v>58637676</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>38880869</v>
+        <v>41871217</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>38880869</v>
+        <v>41871217</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>57108480</v>
+        <v>60983184</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>62053598</v>
+        <v>66418978</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>62053598</v>
+        <v>66418978</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4949401</v>
+        <v>5285209</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>59392812</v>
+        <v>63422508</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>85812330</v>
+        <v>91587513</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>85812330</v>
+        <v>91587513</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5147377</v>
+        <v>5496617</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>61768524</v>
+        <v>65959404</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>110171884</v>
+        <v>117392522</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>110171884</v>
+        <v>117392522</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>52800000</v>
+        <v>56382384</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1378032</v>
+        <v>1485081</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>10171884</v>
+        <v>17392522</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>126598267</v>
@@ -1280,7 +1280,7 @@
         <v>273401733</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>136770151</v>
+        <v>143990789</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>운정 입주·디딤돌 28,000만 · 집마련 저축 중단 · 월 여유 ~63만</t>
+          <t>운정 입주·디딤돌 28,000만 · 집마련 저축 중단 · 월 여유 ~73만</t>
         </is>
       </c>
     </row>
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4576000</v>
+        <v>4886473</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>54912000</v>
+        <v>58637676</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1554032</v>
+        <v>1673022</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>804032</v>
+        <v>923022</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>29292669</v>
+        <v>38140261</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>133370149</v>
@@ -1344,7 +1344,7 @@
         <v>266629851</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>162662818</v>
+        <v>171510410</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -1387,19 +1387,19 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>57108480</v>
+        <v>60983184</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>887072</v>
+        <v>1018481</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>237072</v>
+        <v>368481</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>40801123</v>
+        <v>51467560</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>140320212</v>
@@ -1408,7 +1408,7 @@
         <v>259679788</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>181121335</v>
+        <v>191787772</v>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4949401</v>
+        <v>5285209</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>59392812</v>
+        <v>63422508</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1077433</v>
+        <v>1221758</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>427433</v>
+        <v>571758</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>54911297</v>
+        <v>67599355</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>147453145</v>
@@ -1472,7 +1472,7 @@
         <v>252546855</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>202364442</v>
+        <v>215052500</v>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>5147377</v>
+        <v>5496617</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>61768524</v>
+        <v>65959404</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1275409</v>
+        <v>1433166</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>625409</v>
+        <v>783166</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>71781419</v>
+        <v>86705265</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>154773762</v>
@@ -1536,7 +1536,7 @@
         <v>245226238</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>226555181</v>
+        <v>241479027</v>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
@@ -1579,19 +1579,19 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5353272</v>
+        <v>5716482</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>64239264</v>
+        <v>68597784</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1481304</v>
+        <v>1653031</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>831304</v>
+        <v>1003031</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>91577409</v>
+        <v>108963157</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>162286996</v>
@@ -1600,7 +1600,7 @@
         <v>237713004</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>253864405</v>
+        <v>271250153</v>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>5567403</v>
+        <v>5945141</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>66808836</v>
+        <v>71341692</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1695435</v>
+        <v>1881690</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>1045435</v>
+        <v>1231690</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>114473229</v>
+        <v>134559485</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>169997922</v>
@@ -1664,7 +1664,7 @@
         <v>230002078</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>284471151</v>
+        <v>304557407</v>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
@@ -1707,19 +1707,19 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>5790099</v>
+        <v>6182947</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>69481188</v>
+        <v>74195364</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1918131</v>
+        <v>2119496</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>1268131</v>
+        <v>1469496</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>140651236</v>
+        <v>163689703</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>177911739</v>
@@ -1728,7 +1728,7 @@
         <v>222088261</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>318562975</v>
+        <v>341601442</v>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>6021703</v>
+        <v>6430265</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>72260436</v>
+        <v>77163180</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2149735</v>
+        <v>2366814</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>1499735</v>
+        <v>1716814</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>170302559</v>
+        <v>196558638</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>186033783</v>
@@ -1788,7 +1788,7 @@
         <v>213966217</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>356336342</v>
+        <v>382592421</v>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>6262571</v>
+        <v>6687476</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>75150852</v>
+        <v>80249712</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2390603</v>
+        <v>2624025</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1740603</v>
+        <v>1974025</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>203627486</v>
+        <v>233380924</v>
       </c>
       <c r="K18" s="8" t="n">
         <v>194369535</v>
@@ -1848,7 +1848,7 @@
         <v>205630465</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>397997021</v>
+        <v>427750459</v>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>고정비 123만</t>
+          <t>고정비 140만·여친 고정 포함</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>저축 208만/월</t>
+          <t>저축 218만/월</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>여유 63만 배분</t>
+          <t>여유 73만 배분</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="C4" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1321968</v>
+        <v>1513451</v>
       </c>
       <c r="C5" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1328032</v>
+        <v>1435081</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
       <c r="C13" t="n">
-        <v>1378032</v>
+        <v>1485081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="E18" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="F18" t="n">
-        <v>1378032</v>
+        <v>1485081</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E19" t="n">
-        <v>887072</v>
+        <v>1018481</v>
       </c>
       <c r="F19" t="n">
-        <v>1637072</v>
+        <v>1768481</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E20" t="n">
-        <v>337072</v>
+        <v>468481</v>
       </c>
       <c r="F20" t="n">
-        <v>1087072</v>
+        <v>1218481</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E21" t="n">
-        <v>237072</v>
+        <v>368481</v>
       </c>
       <c r="F21" t="n">
-        <v>887072</v>
+        <v>1018481</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4949401</v>
+        <v>5285209</v>
       </c>
       <c r="E22" t="n">
-        <v>327433</v>
+        <v>471758</v>
       </c>
       <c r="F22" t="n">
-        <v>1077433</v>
+        <v>1221758</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E23" t="n">
-        <v>37072</v>
+        <v>168481</v>
       </c>
       <c r="F23" t="n">
-        <v>587072</v>
+        <v>718481</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2811,7 +2811,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>방법 C (자동 동기화)</t>
+          <t>방법 C (자동 · 재무앱 OAuth)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pip install gspread google-auth</t>
+          <t>config/credentials.json 준비 (setup.py와 동일)</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Google Cloud에서 서비스 계정 + JSON 키 발급</t>
+          <t>python scripts/upload_to_google_sheets.py --oauth</t>
         </is>
       </c>
     </row>
@@ -2848,57 +2848,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>credentials/google_service_account.json 에 저장</t>
+          <t>기존 시트에 추가: --oauth --id=스프레드시트ID</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>python scripts/upload_to_google_sheets.py 실행</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>엑셀 서식·색은 구글에서 일부 달라질 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>갱신</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>엑셀 서식·색은 구글에서 일부 달라질 수 있음</t>
+          <t>로컬에서 build 스크립트 재실행 후 다시 업로드</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>갱신</t>
+          <t>관련 파일</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
-        <is>
-          <t>로컬에서 build 스크립트 재실행 후 다시 업로드</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>관련 파일</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
         <is>
           <t>sheets/인생플랜.xlsx — 월예산·고정비 상세</t>
         </is>
